--- a/artfynd/A 51733-2023 artfynd.xlsx
+++ b/artfynd/A 51733-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51733-2023 artfynd.xlsx
+++ b/artfynd/A 51733-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70140177</v>
+        <v>113110792</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>97326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>650 m ONO om Axsjöns ostspets, Upl</t>
+          <t>Uvberget-Tallmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615977.0629175911</v>
+        <v>616215</v>
       </c>
       <c r="R2" t="n">
-        <v>6648964.111171228</v>
+        <v>6648865</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,23 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113110792</v>
+        <v>113110794</v>
       </c>
       <c r="B3" t="n">
         <v>97326</v>
@@ -836,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616215</v>
+        <v>616032</v>
       </c>
       <c r="R3" t="n">
-        <v>6648865</v>
+        <v>6648894</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -898,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113110794</v>
+        <v>113110789</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
+        <v>96289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616032</v>
+        <v>615893</v>
       </c>
       <c r="R4" t="n">
-        <v>6648894</v>
+        <v>6649026</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1000,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113110789</v>
+        <v>113110795</v>
       </c>
       <c r="B5" t="n">
-        <v>96289</v>
+        <v>97326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615893</v>
+        <v>616004</v>
       </c>
       <c r="R5" t="n">
-        <v>6649026</v>
+        <v>6648886</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1102,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113110795</v>
+        <v>113110793</v>
       </c>
       <c r="B6" t="n">
         <v>97326</v>
@@ -1142,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616004</v>
+        <v>616130</v>
       </c>
       <c r="R6" t="n">
-        <v>6648886</v>
+        <v>6648906</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1204,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113110793</v>
+        <v>113110796</v>
       </c>
       <c r="B7" t="n">
         <v>97326</v>
@@ -1244,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616130</v>
+        <v>616003</v>
       </c>
       <c r="R7" t="n">
-        <v>6648906</v>
+        <v>6648898</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1306,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113110796</v>
+        <v>113131523</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>97650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,14 +1323,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uvberget-Tallmossen, Upl</t>
+          <t>Uvberget, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616003</v>
+        <v>616209</v>
       </c>
       <c r="R8" t="n">
-        <v>6648898</v>
+        <v>6648882</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1390,25 +1371,26 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113131523</v>
+        <v>113131527</v>
       </c>
       <c r="B9" t="n">
         <v>97650</v>
@@ -1448,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616209</v>
+        <v>615847</v>
       </c>
       <c r="R9" t="n">
-        <v>6648882</v>
+        <v>6649181</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1511,7 +1493,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113131527</v>
+        <v>113131526</v>
       </c>
       <c r="B10" t="n">
         <v>97650</v>
@@ -1551,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615847</v>
+        <v>615832</v>
       </c>
       <c r="R10" t="n">
-        <v>6649181</v>
+        <v>6649032</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1614,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113131526</v>
+        <v>113131537</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
+        <v>99909</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1608,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615832</v>
+        <v>616151</v>
       </c>
       <c r="R11" t="n">
-        <v>6649032</v>
+        <v>6648934</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1698,7 +1680,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1717,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113131537</v>
+        <v>113131529</v>
       </c>
       <c r="B12" t="n">
-        <v>99909</v>
+        <v>97650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,25 +1710,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616151</v>
+        <v>615859</v>
       </c>
       <c r="R12" t="n">
-        <v>6648934</v>
+        <v>6649208</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1819,7 +1800,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113131529</v>
+        <v>113131524</v>
       </c>
       <c r="B13" t="n">
         <v>97650</v>
@@ -1859,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615859</v>
+        <v>616151</v>
       </c>
       <c r="R13" t="n">
-        <v>6649208</v>
+        <v>6648924</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1903,6 +1884,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1921,7 +1903,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113131524</v>
+        <v>113131525</v>
       </c>
       <c r="B14" t="n">
         <v>97650</v>
@@ -1961,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616151</v>
+        <v>615790</v>
       </c>
       <c r="R14" t="n">
-        <v>6648924</v>
+        <v>6648950</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2024,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113131525</v>
+        <v>114461484</v>
       </c>
       <c r="B15" t="n">
         <v>97650</v>
@@ -2060,14 +2042,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Uvberget, Upl</t>
+          <t>Uvberget (4), Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615790</v>
+        <v>615832</v>
       </c>
       <c r="R15" t="n">
-        <v>6648950</v>
+        <v>6649031</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2092,6 +2074,11 @@
           <t>Vittinge</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C-Heb-0313</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>2023-11-05</t>
@@ -2108,129 +2095,21 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Ivar Anderberg</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>114461484</v>
-      </c>
-      <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Uvberget (4), Upl</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>615832</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6649031</v>
-      </c>
-      <c r="S16" t="n">
-        <v>15</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Vittinge</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>C-Heb-0313</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 51733-2023 artfynd.xlsx
+++ b/artfynd/A 51733-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113110792</v>
+        <v>70140177</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uvberget-Tallmossen, Upl</t>
+          <t>650 m ONO om Axsjöns ostspets, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616215</v>
+        <v>615977.0629175911</v>
       </c>
       <c r="R2" t="n">
-        <v>6648865</v>
+        <v>6648964.111171228</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>1997-12-31</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +780,23 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113110794</v>
+        <v>113110792</v>
       </c>
       <c r="B3" t="n">
         <v>97326</v>
@@ -817,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616032</v>
+        <v>616215</v>
       </c>
       <c r="R3" t="n">
-        <v>6648894</v>
+        <v>6648865</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113110789</v>
+        <v>113110794</v>
       </c>
       <c r="B4" t="n">
-        <v>96289</v>
+        <v>97326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615893</v>
+        <v>616032</v>
       </c>
       <c r="R4" t="n">
-        <v>6649026</v>
+        <v>6648894</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113110795</v>
+        <v>113110789</v>
       </c>
       <c r="B5" t="n">
-        <v>97326</v>
+        <v>96289</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1012,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616004</v>
+        <v>615893</v>
       </c>
       <c r="R5" t="n">
-        <v>6648886</v>
+        <v>6649026</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113110793</v>
+        <v>113110795</v>
       </c>
       <c r="B6" t="n">
         <v>97326</v>
@@ -1123,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616130</v>
+        <v>616004</v>
       </c>
       <c r="R6" t="n">
-        <v>6648906</v>
+        <v>6648886</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113110796</v>
+        <v>113110793</v>
       </c>
       <c r="B7" t="n">
         <v>97326</v>
@@ -1225,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616003</v>
+        <v>616130</v>
       </c>
       <c r="R7" t="n">
-        <v>6648898</v>
+        <v>6648906</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113131523</v>
+        <v>113110796</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
+        <v>97326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,14 +1342,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uvberget, Upl</t>
+          <t>Uvberget-Tallmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616209</v>
+        <v>616003</v>
       </c>
       <c r="R8" t="n">
-        <v>6648882</v>
+        <v>6648898</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,26 +1390,25 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113131527</v>
+        <v>113131523</v>
       </c>
       <c r="B9" t="n">
         <v>97650</v>
@@ -1430,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615847</v>
+        <v>616209</v>
       </c>
       <c r="R9" t="n">
-        <v>6649181</v>
+        <v>6648882</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1493,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113131526</v>
+        <v>113131527</v>
       </c>
       <c r="B10" t="n">
         <v>97650</v>
@@ -1533,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615832</v>
+        <v>615847</v>
       </c>
       <c r="R10" t="n">
-        <v>6649032</v>
+        <v>6649181</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1596,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113131537</v>
+        <v>113131526</v>
       </c>
       <c r="B11" t="n">
-        <v>99909</v>
+        <v>97650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1608,25 +1626,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616151</v>
+        <v>615832</v>
       </c>
       <c r="R11" t="n">
-        <v>6648934</v>
+        <v>6649032</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1680,6 +1698,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1698,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113131529</v>
+        <v>113131537</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
+        <v>99909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1710,25 +1729,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>615859</v>
+        <v>616151</v>
       </c>
       <c r="R12" t="n">
-        <v>6649208</v>
+        <v>6648934</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,7 +1819,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113131524</v>
+        <v>113131529</v>
       </c>
       <c r="B13" t="n">
         <v>97650</v>
@@ -1840,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>616151</v>
+        <v>615859</v>
       </c>
       <c r="R13" t="n">
-        <v>6648924</v>
+        <v>6649208</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1884,7 +1903,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1903,7 +1921,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113131525</v>
+        <v>113131524</v>
       </c>
       <c r="B14" t="n">
         <v>97650</v>
@@ -1943,10 +1961,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>615790</v>
+        <v>616151</v>
       </c>
       <c r="R14" t="n">
-        <v>6648950</v>
+        <v>6648924</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,7 +2024,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114461484</v>
+        <v>113131525</v>
       </c>
       <c r="B15" t="n">
         <v>97650</v>
@@ -2042,14 +2060,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Uvberget (4), Upl</t>
+          <t>Uvberget, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615832</v>
+        <v>615790</v>
       </c>
       <c r="R15" t="n">
-        <v>6649031</v>
+        <v>6648950</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2074,11 +2092,6 @@
           <t>Vittinge</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>C-Heb-0313</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>2023-11-05</t>
@@ -2095,21 +2108,129 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ivar Anderberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114461484</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97650</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Uvberget (4), Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>615832</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6649031</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C-Heb-0313</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-11-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-11-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Ingvar Sundh</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Ivar Anderberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 51733-2023 artfynd.xlsx
+++ b/artfynd/A 51733-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70140177</v>
+        <v>113110792</v>
       </c>
       <c r="B2" t="n">
-        <v>97913</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>650 m ONO om Axsjöns ostspets, Upl</t>
+          <t>Uvberget-Tallmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615977</v>
+        <v>616215</v>
       </c>
       <c r="R2" t="n">
-        <v>6648964</v>
+        <v>6648865</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -736,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113110792</v>
+        <v>113110793</v>
       </c>
       <c r="B3" t="n">
-        <v>97326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616215</v>
+        <v>616131</v>
       </c>
       <c r="R3" t="n">
-        <v>6648865</v>
+        <v>6648906</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -882,12 +872,7 @@
         <v>113110794</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113110789</v>
+        <v>113110795</v>
       </c>
       <c r="B5" t="n">
-        <v>96289</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615893</v>
+        <v>616004</v>
       </c>
       <c r="R5" t="n">
-        <v>6649026</v>
+        <v>6648887</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113110795</v>
+        <v>113110796</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616004</v>
+        <v>616002</v>
       </c>
       <c r="R6" t="n">
-        <v>6648886</v>
+        <v>6648899</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113110793</v>
+        <v>113131523</v>
       </c>
       <c r="B7" t="n">
-        <v>97326</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Uvberget-Tallmossen, Upl</t>
+          <t>Uvberget, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616130</v>
+        <v>616209</v>
       </c>
       <c r="R7" t="n">
-        <v>6648906</v>
+        <v>6648882</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1269,33 +1239,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113110796</v>
+        <v>113131524</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,14 +1289,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uvberget-Tallmossen, Upl</t>
+          <t>Uvberget, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616003</v>
+        <v>616151</v>
       </c>
       <c r="R8" t="n">
-        <v>6648898</v>
+        <v>6648924</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,33 +1337,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113131523</v>
+        <v>113131525</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616209</v>
+        <v>615790</v>
       </c>
       <c r="R9" t="n">
-        <v>6648882</v>
+        <v>6648950</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1492,15 +1454,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113131527</v>
+        <v>113131526</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,10 +1489,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>615847</v>
+        <v>615832</v>
       </c>
       <c r="R10" t="n">
-        <v>6649181</v>
+        <v>6649032</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1595,15 +1552,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113131526</v>
+        <v>113131527</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>615832</v>
+        <v>615847</v>
       </c>
       <c r="R11" t="n">
-        <v>6649032</v>
+        <v>6649181</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1698,37 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113131537</v>
+        <v>113131529</v>
       </c>
       <c r="B12" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616151</v>
+        <v>615859</v>
       </c>
       <c r="R12" t="n">
-        <v>6648934</v>
+        <v>6649208</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,53 +1747,44 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113131529</v>
+        <v>70140177</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98054</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Uvberget, Upl</t>
+          <t>650 m ONO om Axsjöns ostspets, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>615859</v>
+        <v>615977</v>
       </c>
       <c r="R13" t="n">
-        <v>6649208</v>
+        <v>6648964</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1870,12 +1808,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>1997-12-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1890,62 +1833,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113131524</v>
+        <v>113110789</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Uvberget, Upl</t>
+          <t>Uvberget-Tallmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616151</v>
+        <v>615893</v>
       </c>
       <c r="R14" t="n">
-        <v>6648924</v>
+        <v>6649026</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1986,56 +1928,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113131525</v>
+        <v>113131537</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>615790</v>
+        <v>616151</v>
       </c>
       <c r="R15" t="n">
-        <v>6648950</v>
+        <v>6648934</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2089,7 +2025,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2105,117 +2040,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>114461484</v>
-      </c>
-      <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Uvberget (4), Upl</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>615832</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6649031</v>
-      </c>
-      <c r="S16" t="n">
-        <v>15</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Vittinge</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>C-Heb-0313</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Ivar Anderberg</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51733-2023 artfynd.xlsx
+++ b/artfynd/A 51733-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110792</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110794</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110795</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110796</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131523</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1388,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131524</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1451,6 +1491,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131526</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131529</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70140177</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110789</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,8 +2110,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113131537</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>